--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121777341</v>
+        <v>121776961</v>
       </c>
       <c r="B6" t="n">
-        <v>78352</v>
+        <v>56569</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,41 +1136,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615793</v>
+        <v>615689</v>
       </c>
       <c r="R6" t="n">
-        <v>6658375</v>
+        <v>6658447</v>
       </c>
       <c r="S6" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1217,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121776961</v>
+        <v>121777341</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
+        <v>78352</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,49 +1261,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615689</v>
+        <v>615793</v>
       </c>
       <c r="R7" t="n">
-        <v>6658447</v>
+        <v>6658375</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,12 +1349,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121777090</v>
+        <v>121777390</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>92039</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,40 +907,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615764</v>
+        <v>615779</v>
       </c>
       <c r="R4" t="n">
-        <v>6658483</v>
+        <v>6658339</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,29 +985,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121777390</v>
+        <v>121777090</v>
       </c>
       <c r="B5" t="n">
-        <v>92039</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,37 +1019,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615779</v>
+        <v>615764</v>
       </c>
       <c r="R5" t="n">
-        <v>6658339</v>
+        <v>6658483</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,18 +1105,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121777390</v>
+        <v>121777341</v>
       </c>
       <c r="B4" t="n">
-        <v>92039</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615779</v>
+        <v>615793</v>
       </c>
       <c r="R4" t="n">
-        <v>6658339</v>
+        <v>6658375</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121777090</v>
+        <v>121777390</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>92039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,40 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615764</v>
+        <v>615779</v>
       </c>
       <c r="R5" t="n">
-        <v>6658483</v>
+        <v>6658339</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,29 +1097,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121776961</v>
+        <v>121777090</v>
       </c>
       <c r="B6" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,35 +1127,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615689</v>
+        <v>615764</v>
       </c>
       <c r="R6" t="n">
-        <v>6658447</v>
+        <v>6658483</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
+          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121777341</v>
+        <v>121776961</v>
       </c>
       <c r="B7" t="n">
-        <v>78352</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,41 +1248,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615793</v>
+        <v>615689</v>
       </c>
       <c r="R7" t="n">
-        <v>6658375</v>
+        <v>6658447</v>
       </c>
       <c r="S7" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,12 +1349,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121777341</v>
+        <v>121777090</v>
       </c>
       <c r="B4" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,37 +907,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615793</v>
+        <v>615764</v>
       </c>
       <c r="R4" t="n">
-        <v>6658375</v>
+        <v>6658483</v>
       </c>
       <c r="S4" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -976,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,18 +993,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1115,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121777090</v>
+        <v>121777341</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,40 +1140,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615764</v>
+        <v>615793</v>
       </c>
       <c r="R6" t="n">
-        <v>6658483</v>
+        <v>6658375</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,19 +1218,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121777390</v>
+        <v>121776961</v>
       </c>
       <c r="B4" t="n">
-        <v>92039</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,41 +903,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615779</v>
+        <v>615689</v>
       </c>
       <c r="R4" t="n">
-        <v>6658339</v>
+        <v>6658447</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -976,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,12 +1004,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1236,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121776961</v>
+        <v>121777390</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
+        <v>92039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,49 +1261,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615689</v>
+        <v>615779</v>
       </c>
       <c r="R7" t="n">
-        <v>6658447</v>
+        <v>6658339</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,12 +1349,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121776961</v>
+        <v>121777341</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>78365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,49 +903,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615689</v>
+        <v>615793</v>
       </c>
       <c r="R4" t="n">
-        <v>6658447</v>
+        <v>6658375</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,12 +991,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1006,7 @@
         <v>121777090</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1137,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121777341</v>
+        <v>121777390</v>
       </c>
       <c r="B6" t="n">
-        <v>78352</v>
+        <v>92053</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615793</v>
+        <v>615779</v>
       </c>
       <c r="R6" t="n">
-        <v>6658375</v>
+        <v>6658339</v>
       </c>
       <c r="S6" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121777390</v>
+        <v>121776961</v>
       </c>
       <c r="B7" t="n">
-        <v>92039</v>
+        <v>56577</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,41 +1248,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615779</v>
+        <v>615689</v>
       </c>
       <c r="R7" t="n">
-        <v>6658339</v>
+        <v>6658447</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,12 +1349,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121777341</v>
+        <v>121777390</v>
       </c>
       <c r="B4" t="n">
-        <v>78365</v>
+        <v>92055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615793</v>
+        <v>615779</v>
       </c>
       <c r="R4" t="n">
-        <v>6658375</v>
+        <v>6658339</v>
       </c>
       <c r="S4" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121777090</v>
+        <v>121777341</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
+        <v>78367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,40 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615764</v>
+        <v>615793</v>
       </c>
       <c r="R5" t="n">
-        <v>6658483</v>
+        <v>6658375</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,29 +1097,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121777390</v>
+        <v>121776961</v>
       </c>
       <c r="B6" t="n">
-        <v>92053</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,41 +1127,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615779</v>
+        <v>615689</v>
       </c>
       <c r="R6" t="n">
-        <v>6658339</v>
+        <v>6658447</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1208,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121776961</v>
+        <v>121777090</v>
       </c>
       <c r="B7" t="n">
-        <v>56577</v>
+        <v>78631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,35 +1252,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615689</v>
+        <v>615764</v>
       </c>
       <c r="R7" t="n">
-        <v>6658447</v>
+        <v>6658483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1328,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
+          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,6 +1342,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121777390</v>
+        <v>121776961</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>56577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,41 +903,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615779</v>
+        <v>615689</v>
       </c>
       <c r="R4" t="n">
-        <v>6658339</v>
+        <v>6658447</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -976,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121777341</v>
+        <v>121777090</v>
       </c>
       <c r="B5" t="n">
-        <v>78367</v>
+        <v>78632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,37 +1032,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615793</v>
+        <v>615764</v>
       </c>
       <c r="R5" t="n">
-        <v>6658375</v>
+        <v>6658483</v>
       </c>
       <c r="S5" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1104,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,28 +1118,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121776961</v>
+        <v>121777390</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>92056</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,49 +1149,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615689</v>
+        <v>615779</v>
       </c>
       <c r="R6" t="n">
-        <v>6658447</v>
+        <v>6658339</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121777090</v>
+        <v>121777341</v>
       </c>
       <c r="B7" t="n">
-        <v>78631</v>
+        <v>78368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,40 +1265,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615764</v>
+        <v>615793</v>
       </c>
       <c r="R7" t="n">
-        <v>6658483</v>
+        <v>6658375</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,19 +1343,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55237-2024 artfynd.xlsx
+++ b/artfynd/A 55237-2024 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121776961</v>
+        <v>121777090</v>
       </c>
       <c r="B4" t="n">
-        <v>56577</v>
+        <v>78639</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +903,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615689</v>
+        <v>615764</v>
       </c>
       <c r="R4" t="n">
-        <v>6658447</v>
+        <v>6658483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
+          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121777090</v>
+        <v>121776961</v>
       </c>
       <c r="B5" t="n">
-        <v>78632</v>
+        <v>56581</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,30 +1024,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615764</v>
+        <v>615689</v>
       </c>
       <c r="R5" t="n">
-        <v>6658483</v>
+        <v>6658447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På naturvårdssnitslad grovbarkig hällmarkstall, impediment utsnitslat. Ytan ska schackrutehuggas.</t>
+          <t>Vid rotvälta i kanten av hällmarksimpediment. Strax utanför naturvårdssnitsla impediment.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1119,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121777390</v>
+        <v>121777341</v>
       </c>
       <c r="B6" t="n">
-        <v>92056</v>
+        <v>78375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615779</v>
+        <v>615793</v>
       </c>
       <c r="R6" t="n">
-        <v>6658339</v>
+        <v>6658375</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121777341</v>
+        <v>121777390</v>
       </c>
       <c r="B7" t="n">
-        <v>78368</v>
+        <v>92065</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615793</v>
+        <v>615779</v>
       </c>
       <c r="R7" t="n">
-        <v>6658375</v>
+        <v>6658339</v>
       </c>
       <c r="S7" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
